--- a/pandas-prac/pandas-pactise/data-cleaning/cleaned_data.xlsx
+++ b/pandas-prac/pandas-pactise/data-cleaning/cleaned_data.xlsx
@@ -539,7 +539,7 @@
         <v>35</v>
       </c>
       <c r="D5" t="n">
-        <v>80000</v>
+        <v>74000</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-5</v>
+        <v>23</v>
       </c>
       <c r="D10" t="n">
         <v>58000</v>
@@ -695,7 +695,7 @@
         <v>26</v>
       </c>
       <c r="D11" t="n">
-        <v>9999999</v>
+        <v>74000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>200</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
         <v>50000</v>
